--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXI/LTAIPT_A63F21B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXI/LTAIPT_A63F21B.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD5D01C-13A6-4DB2-985C-CC616EB330A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -15,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="134">
   <si>
     <t>48971</t>
   </si>
@@ -72,9 +78,6 @@
   </si>
   <si>
     <t>436165</t>
-  </si>
-  <si>
-    <t>436159</t>
   </si>
   <si>
     <t>436160</t>
@@ -105,19 +108,16 @@
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>6391610</t>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>16084160</t>
   </si>
   <si>
     <t>Departamento de Programación y Presupuesto</t>
@@ -126,22 +126,25 @@
     <t/>
   </si>
   <si>
-    <t>75ACE755BA2B2F3F539F0ACB90B4CA0C</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>6787257</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informaci%c3%b3n%20Presupuestal/Informaci%c3%b3n%20Presupuestal.pdf</t>
-  </si>
-  <si>
-    <t>20/07/2023</t>
+    <t>353AFDC261BFE3076A5F3FCB0F943F26</t>
+  </si>
+  <si>
+    <t>01/04/2024</t>
+  </si>
+  <si>
+    <t>30/06/2024</t>
+  </si>
+  <si>
+    <t>14674325</t>
+  </si>
+  <si>
+    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informacion%20Presupuestal.pdf</t>
+  </si>
+  <si>
+    <t>19/07/2024</t>
+  </si>
+  <si>
+    <t>10002389</t>
   </si>
   <si>
     <t>6</t>
@@ -198,7 +201,7 @@
     <t>Subejercicio</t>
   </si>
   <si>
-    <t>E9A4CE1D7739C4DDD2FE3AE639708194</t>
+    <t>CBFD22E0FE12740EFBE625190DCE854F</t>
   </si>
   <si>
     <t>1000</t>
@@ -207,19 +210,19 @@
     <t>Servicios personales</t>
   </si>
   <si>
-    <t>501206101</t>
+    <t>530132129</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>85645506.28</t>
-  </si>
-  <si>
-    <t>415560594.7</t>
-  </si>
-  <si>
-    <t>2CF20E36FEEF52AEC534E780175BED03</t>
+    <t>318559307.8</t>
+  </si>
+  <si>
+    <t>211572821.2</t>
+  </si>
+  <si>
+    <t>CBFD22E0FE12740E8CDC2D8D5C0224CE</t>
   </si>
   <si>
     <t>2000</t>
@@ -228,16 +231,22 @@
     <t>Materiales y suministros</t>
   </si>
   <si>
-    <t>9112031</t>
-  </si>
-  <si>
-    <t>762952.45</t>
-  </si>
-  <si>
-    <t>8349078.55</t>
-  </si>
-  <si>
-    <t>2CF20E36FEEF52AECC40B12AC7E81564</t>
+    <t>14277549</t>
+  </si>
+  <si>
+    <t>60660</t>
+  </si>
+  <si>
+    <t>14338209</t>
+  </si>
+  <si>
+    <t>5081807.71</t>
+  </si>
+  <si>
+    <t>9256401.29</t>
+  </si>
+  <si>
+    <t>CBFD22E0FE12740EEB85B3EBCFE75841</t>
   </si>
   <si>
     <t>3000</t>
@@ -246,16 +255,22 @@
     <t>Servicios generales</t>
   </si>
   <si>
-    <t>44875950</t>
-  </si>
-  <si>
-    <t>3492570.77</t>
-  </si>
-  <si>
-    <t>41383379.23</t>
-  </si>
-  <si>
-    <t>2CF20E36FEEF52AE77C9DB1AECF7AAA5</t>
+    <t>34194982</t>
+  </si>
+  <si>
+    <t>2745242.04</t>
+  </si>
+  <si>
+    <t>36940224.04</t>
+  </si>
+  <si>
+    <t>13315512.34</t>
+  </si>
+  <si>
+    <t>23624711.7</t>
+  </si>
+  <si>
+    <t>CBFD22E0FE12740EF84B82E3A1E56847</t>
   </si>
   <si>
     <t>4000</t>
@@ -264,10 +279,22 @@
     <t>Transferencias, asignaciones, subsidios y otras ayudas</t>
   </si>
   <si>
-    <t>1400000</t>
-  </si>
-  <si>
-    <t>2CF20E36FEEF52AE02CCA7754F25B3FC</t>
+    <t>2390340</t>
+  </si>
+  <si>
+    <t>-15000</t>
+  </si>
+  <si>
+    <t>2375340</t>
+  </si>
+  <si>
+    <t>644710</t>
+  </si>
+  <si>
+    <t>1730630</t>
+  </si>
+  <si>
+    <t>CBFD22E0FE12740E2AB045C0D16DAC63</t>
   </si>
   <si>
     <t>5000</t>
@@ -276,82 +303,133 @@
     <t>Bienes muebles e inmuebles</t>
   </si>
   <si>
-    <t>8093964</t>
-  </si>
-  <si>
-    <t>69164.06</t>
-  </si>
-  <si>
-    <t>8024799.94</t>
-  </si>
-  <si>
-    <t>20317EA5A79848D2E4EA3A676A48F4C3</t>
-  </si>
-  <si>
-    <t>194845436.4</t>
-  </si>
-  <si>
-    <t>306360664.6</t>
-  </si>
-  <si>
-    <t>20317EA5A79848D2B514FCEBF2C268C2</t>
-  </si>
-  <si>
-    <t>39811.2</t>
-  </si>
-  <si>
-    <t>9151842.2</t>
-  </si>
-  <si>
-    <t>5546253.33</t>
-  </si>
-  <si>
-    <t>3605588.87</t>
-  </si>
-  <si>
-    <t>20317EA5A79848D27335B10110122D3E</t>
-  </si>
-  <si>
-    <t>-39800.25</t>
-  </si>
-  <si>
-    <t>44836149.75</t>
-  </si>
-  <si>
-    <t>9025697.65</t>
-  </si>
-  <si>
-    <t>35810452.1</t>
-  </si>
-  <si>
-    <t>20317EA5A79848D2488DABE3915F83C3</t>
-  </si>
-  <si>
-    <t>1617370.69</t>
-  </si>
-  <si>
-    <t>3017370.69</t>
-  </si>
-  <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>3011370.69</t>
-  </si>
-  <si>
-    <t>20317EA5A79848D25048589F46F73DA6</t>
-  </si>
-  <si>
-    <t>170300.06</t>
-  </si>
-  <si>
-    <t>7923663.94</t>
+    <t>10027774</t>
+  </si>
+  <si>
+    <t>1268934</t>
+  </si>
+  <si>
+    <t>11296708</t>
+  </si>
+  <si>
+    <t>235728.31</t>
+  </si>
+  <si>
+    <t>11060979.69</t>
+  </si>
+  <si>
+    <t>B9FD5554FDAFFCF555BABB8D354A3F0C</t>
+  </si>
+  <si>
+    <t>62000</t>
+  </si>
+  <si>
+    <t>14339549</t>
+  </si>
+  <si>
+    <t>4192010.49</t>
+  </si>
+  <si>
+    <t>10147538.51</t>
+  </si>
+  <si>
+    <t>B9FD5554FDAFFCF53690CB8166E8E3F1</t>
+  </si>
+  <si>
+    <t>1424733.25</t>
+  </si>
+  <si>
+    <t>35619715.25</t>
+  </si>
+  <si>
+    <t>9001766.33</t>
+  </si>
+  <si>
+    <t>26617948.92</t>
+  </si>
+  <si>
+    <t>B9FD5554FDAFFCF5E76FDFBBE452A6E2</t>
+  </si>
+  <si>
+    <t>634710</t>
+  </si>
+  <si>
+    <t>1740630</t>
+  </si>
+  <si>
+    <t>B9FD5554FDAFFCF5DD8C8EC9673332CE</t>
+  </si>
+  <si>
+    <t>215946758.8</t>
+  </si>
+  <si>
+    <t>314185370.3</t>
+  </si>
+  <si>
+    <t>B9FD5554FDAFFCF5E7ABE3D6FD745166</t>
+  </si>
+  <si>
+    <t>830290</t>
+  </si>
+  <si>
+    <t>10858064</t>
+  </si>
+  <si>
+    <t>225172.31</t>
+  </si>
+  <si>
+    <t>10632891.69</t>
+  </si>
+  <si>
+    <t>0B0971987B1FB31B3176D19ACC017A5B</t>
+  </si>
+  <si>
+    <t>105395961.6</t>
+  </si>
+  <si>
+    <t>424736167.4</t>
+  </si>
+  <si>
+    <t>0B0971987B1FB31BBAE91E1797A24735</t>
+  </si>
+  <si>
+    <t>549309.14</t>
+  </si>
+  <si>
+    <t>13728239.86</t>
+  </si>
+  <si>
+    <t>0B0971987B1FB31B0DAD9ACEB470BE26</t>
+  </si>
+  <si>
+    <t>330944.17</t>
+  </si>
+  <si>
+    <t>34525926.17</t>
+  </si>
+  <si>
+    <t>3647896.62</t>
+  </si>
+  <si>
+    <t>30878029.55</t>
+  </si>
+  <si>
+    <t>0B0971987B1FB31B6056FC93874DA895</t>
+  </si>
+  <si>
+    <t>624000</t>
+  </si>
+  <si>
+    <t>1766340</t>
+  </si>
+  <si>
+    <t>0B0971987B1FB31B84F4512A1C9EFE08</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -450,6 +528,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -465,44 +546,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -530,14 +611,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -565,6 +663,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -576,192 +691,167 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="70.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="169" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -778,7 +868,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -793,7 +883,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -813,16 +903,13 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -847,13 +934,10 @@
       <c r="I5" t="s">
         <v>20</v>
       </c>
-      <c r="J5" t="s">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -863,72 +947,65 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="I8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A6:I6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -941,12 +1018,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="46.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
@@ -965,398 +1042,558 @@
         <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
         <v>43</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>44</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>45</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>46</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>47</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>48</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>49</v>
-      </c>
-      <c r="J2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>109</v>
+      <c r="F17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXI/LTAIPT_A63F21B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXI/LTAIPT_A63F21B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD5D01C-13A6-4DB2-985C-CC616EB330A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B664FBF5-4CF6-46D2-A378-5B7F076616E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,34 +114,34 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>B0A2F1441CD203104F728E10885C30DE</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t>16084160</t>
   </si>
   <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/3er%20Trimestre/Informacion%20Presupuestal.pdf</t>
+  </si>
+  <si>
     <t>Departamento de Programación y Presupuesto</t>
   </si>
   <si>
+    <t>18/10/2024</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>353AFDC261BFE3076A5F3FCB0F943F26</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
     <t>14674325</t>
-  </si>
-  <si>
-    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informacion%20Presupuestal.pdf</t>
-  </si>
-  <si>
-    <t>19/07/2024</t>
   </si>
   <si>
     <t>10002389</t>
@@ -976,31 +976,31 @@
     </row>
     <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1118,7 +1118,7 @@
     </row>
     <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>59</v>
@@ -1150,7 +1150,7 @@
     </row>
     <row r="5" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>66</v>
@@ -1182,7 +1182,7 @@
     </row>
     <row r="6" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>74</v>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>82</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>90</v>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="9" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>98</v>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="10" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>103</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="11" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>108</v>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="12" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>111</v>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="13" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>114</v>
